--- a/reports/Master_Comparison_Report.xlsx
+++ b/reports/Master_Comparison_Report.xlsx
@@ -8,6 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MASTER_SUMMARY" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALL_DIFFERENCES" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALL_MISSING_RECORDS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALL_ZERO_VALUES" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALL_DUPLICATES" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,6 +417,1948 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Differences</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Missing Records</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Zero Values</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Duplicates</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>00022</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20260524</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>00022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>00022</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20260607</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>00023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20260524</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>00023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>00023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20260607</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>00221</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20260524</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>00221</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>00221</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260607</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AC FILE MISSING</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>00221</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260614</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>01254</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20260524</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>01254</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>01254</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>20260607</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>01480</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20260524</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>01480</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>01480</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20260607</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>05450</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20260524</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>05450</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>05450</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>20260607</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>06796</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20260524</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>06796</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>06796</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20260607</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>07347</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>20260524</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>07347</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>07347</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>20260607</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>08107</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>20260524</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>08107</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>08107</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>20260607</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>08154</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>20260524</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>08154</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>08154</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>20260607</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Node</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Difference Type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CB Value</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>AC Value</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Missing Attribute In AC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Poll/Labor/TM0(type=DAILY)/TM1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>pay</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>97.81</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>00022</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Missing Attribute In AC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Poll/Labor/TM0(type=DAILY)/TM1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>pay</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>97.81</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>00221</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Missing Attribute In AC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Poll/Labor/TM0(type=DAILY)/TM1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>pay</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>97.81</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>01254</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20260524</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Missing Attribute In AC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Poll/Labor/TM0(type=DAILY)/TM1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>pay</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>97.81</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>01254</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20260607</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Value Mismatch</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Poll/Labor/TM0(type=DAILY)/TM1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>pay</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>97.81</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>999.99</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>01480</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Value Mismatch</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Poll/Labor/TM0(type=DAILY)/TM1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>pay</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>97.81</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>999.99</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>01480</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20260607</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Missing Attribute In AC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Poll/Labor/TM0(type=DAILY)/TM1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>pay</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>97.81</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>06796</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20260524</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Missing Attribute In AC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Poll/Labor/TM0(type=DAILY)/TM1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>pay</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>97.81</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>06796</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Value Mismatch</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Poll/Labor/TM0(type=DAILY)/TM1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>pay</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>97.81</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>999.99</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>08107</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20260524</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Value Mismatch</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Poll/Labor/TM0(type=DAILY)/TM1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>pay</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>97.81</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>999.99</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>08107</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Missing Attribute In AC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Poll/Labor/TM0(type=DAILY)/TM1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>pay</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>97.81</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>08154</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20260607</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Node</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Missing In</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>00022</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>20260607</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00023</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>05450</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20260607</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>07347</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20260607</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>08154</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Node</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Poll/Labor/TM0(type=DAILY)/TM1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pay</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>00023</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>20260524</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Poll/Labor/TM0(type=DAILY)/TM1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pay</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>00221</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20260614</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Poll/Labor/TM0(type=DAILY)/TM1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>pay</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>01254</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Poll/Labor/TM0(type=DAILY)/TM1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>pay</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>05450</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>20260524</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Poll/Labor/TM0(type=DAILY)/TM1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>200486637_50003</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>pay</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>06796</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>20260607</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>

--- a/reports/Master_Comparison_Report.xlsx
+++ b/reports/Master_Comparison_Report.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,25 +433,35 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>CB File</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>AC File</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Differences</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Missing Records</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Zero Values</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Duplicates</t>
         </is>
@@ -470,19 +480,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_00022_20260524.xml</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_00022_20260524.xml</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -499,19 +519,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_00022_20260531.xml</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_00022_20260531.xml</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -528,19 +558,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_00022_20260607.xml</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_00022_20260607.xml</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -557,19 +597,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_00023_20260524.xml</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_00023_20260524.xml</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -586,19 +636,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_00023_20260531.xml</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_00023_20260531.xml</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -615,19 +675,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_00023_20260607.xml</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_00023_20260607.xml</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -644,19 +714,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_00221_20260524.xml</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_00221_20260524.xml</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -673,19 +753,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_00221_20260531.xml</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_00221_20260531.xml</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -702,19 +792,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_00221_20260607.xml</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>AC FILE MISSING</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -731,19 +831,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_00221_20260614.xml</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_00221_20260614.xml</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -760,19 +870,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_01254_20260524.xml</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_01254_20260524.xml</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -789,19 +909,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_01254_20260531.xml</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_01254_20260531.xml</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
       <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -818,19 +948,29 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_01254_20260607.xml</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_01254_20260607.xml</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -847,19 +987,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_01480_20260524.xml</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_01480_20260524.xml</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -876,19 +1026,29 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_01480_20260531.xml</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_01480_20260531.xml</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -905,19 +1065,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_01480_20260607.xml</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_01480_20260607.xml</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -934,19 +1104,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_05450_20260524.xml</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_05450_20260524.xml</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
       <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>1</v>
       </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -963,19 +1143,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_05450_20260531.xml</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_05450_20260531.xml</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -992,19 +1182,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_05450_20260607.xml</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_05450_20260607.xml</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>1</v>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1021,19 +1221,29 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_06796_20260524.xml</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_06796_20260524.xml</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
       <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1050,19 +1260,29 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_06796_20260531.xml</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_06796_20260531.xml</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>1</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1079,19 +1299,29 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_06796_20260607.xml</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_06796_20260607.xml</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
       <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" t="n">
+      <c r="I23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1108,19 +1338,29 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_07347_20260524.xml</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_07347_20260524.xml</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1137,19 +1377,29 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_07347_20260531.xml</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_07347_20260531.xml</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1166,19 +1416,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_07347_20260607.xml</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_07347_20260607.xml</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
         <v>1</v>
       </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1195,19 +1455,29 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_08107_20260524.xml</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_08107_20260524.xml</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
       <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1224,19 +1494,29 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_08107_20260531.xml</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_08107_20260531.xml</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1253,19 +1533,29 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_08107_20260607.xml</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_08107_20260607.xml</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1282,19 +1572,29 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_08154_20260524.xml</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_08154_20260524.xml</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1311,19 +1611,29 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_08154_20260531.xml</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_08154_20260531.xml</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
         <v>1</v>
       </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1340,19 +1650,29 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>PAYROLL_EXPORT_08154_20260607.xml</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PAYROLL_EXPORT_08154_20260607.xml</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>1</v>
       </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
       <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>0</v>
       </c>
     </row>
